--- a/Votaciones.xlsx
+++ b/Votaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Downloads\proyecto02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560B251A-A891-49C1-A0A4-71384080A9A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630D9CA0-8AFE-46CB-B54F-23B964B47F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C6324BDF-C4C3-4533-A295-7FBD5EF949F4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>LIMA / LIMA / SAN JUAN DE LURIGANCHO</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>DIRECCIÓN</t>
+  </si>
+  <si>
+    <t>LIMA / LIMA / SANTA ANITA</t>
   </si>
 </sst>
 </file>
@@ -434,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A63E95DE-C94E-4B39-AD7D-8E0E6AB21499}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.5546875" customWidth="1"/>
@@ -475,7 +478,13 @@
         <v>15121313</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -484,6 +493,14 @@
       </c>
       <c r="B4" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>41236587</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
